--- a/reports/historical_reports_EMTest.xlsx
+++ b/reports/historical_reports_EMTest.xlsx
@@ -12,6 +12,11 @@
     <sheet name="20260714-160215" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="20260714-161227" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="20260714-164003" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="20260714-184706" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="20260714-191734" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="20260714-210707" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="20260714-220721" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="20260714-223126" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,6 +874,452 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-11T16:58:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-14T16:58:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.039831</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.992883</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.323369</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.326385</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-15.266855</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-15.330297</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-16.298512</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-18.144145</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.054722</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.088014</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.010818</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.000753</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.87258</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>16.833645</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3722</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>55.19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2651,4 +3102,1788 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-07T13:11:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-14T13:11:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.035756</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.850221</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.332378</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.332767</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-5.735411</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-5.880574</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-6.472005</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-12.234665</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.069493</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.222579</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.986483</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.000723</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-1.129423</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>30.207581</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>10656</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5982</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>56.14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-14T13:11:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-14T13:11:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.260201</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.974441</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.699313</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.7087059999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-4.960115</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-5.256091</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-9.033614</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-3.357953</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.290189</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.82538</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.9862919999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.000932</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-1.635778</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>52.877446</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>83490</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>38320</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-07T13:11:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-14T13:11:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.035756</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.850221</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.332378</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.332767</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-5.735411</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-5.880574</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-6.472005</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-12.234665</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.069493</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.222579</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.986483</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.000723</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-1.129423</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>30.207581</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>10656</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5982</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>56.14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-14T16:17:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-14T16:17:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.303037</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.98763</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.64519</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.663757</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-6.537689</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-6.705348</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-10.742352</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-2.928212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.337281</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.908107</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.976546</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.000946</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-1.306413</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>48.57301</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>80574</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>43275</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>37299</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>53.71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reports/historical_reports_EMTest.xlsx
+++ b/reports/historical_reports_EMTest.xlsx
@@ -17,6 +17,10 @@
     <sheet name="20260714-210707" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="20260714-220721" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="20260714-223126" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="20260715-024911" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="20260715-171707" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="20260715-191345" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="20260715-191632" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1320,6 +1324,1808 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:13:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:13:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.013213</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.8017609999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.38399</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.387674</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-4.231867</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-4.324643</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-6.070588</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-15.24518</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.052591</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.061771</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.01751</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.000672</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-1.506135</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>26.853741</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>57.78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-13T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.01945</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.972252</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.020159</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.020358</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-179.912434</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-178.935995</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-12.108831</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-25.026106</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.03885</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.767637</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.971458</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.0008</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.040579</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>11.72066</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>55.49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-08T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-93.594872</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.304378</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.304378</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.344039</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.348338</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-1.054549</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-1.209221</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-1.370433</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.602158</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.505479</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0567</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.95482</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.004768</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.462129</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>35.087911</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>58.81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
